--- a/www/profiles/profile-Wine-zgpr-400.xlsx
+++ b/www/profiles/profile-Wine-zgpr-400.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Workdir\Metabolomic\WAP-NMR\Manips\JC-DUB-400\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Workdir\Metabolomic\NMRProcFlow\git\RnmrQuant1D\RnmrQuant1D_UI\www\profiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1E1C40E-5A2C-4DEA-9582-95EF6A17FA62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20C49507-4E9A-4755-9CC5-BB19F4947D52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-29670" yWindow="-375" windowWidth="28155" windowHeight="14475" xr2:uid="{524AC9D9-352A-4B49-9285-9FC9260D37F8}"/>
+    <workbookView xWindow="2130" yWindow="2445" windowWidth="21600" windowHeight="11235" xr2:uid="{524AC9D9-352A-4B49-9285-9FC9260D37F8}"/>
   </bookViews>
   <sheets>
     <sheet name="profile-zgpr-400" sheetId="1" r:id="rId1"/>
@@ -1343,10 +1343,10 @@
         <v>1.175</v>
       </c>
       <c r="D36" s="5">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E36" s="5">
-        <v>0.99</v>
+        <v>2</v>
       </c>
       <c r="F36" s="5">
         <v>50</v>
